--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/IOWA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/IOWA_2020.xlsx
@@ -1968,7 +1968,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C90">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C118">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C122">
@@ -5557,7 +5557,7 @@
         <v>17</v>
       </c>
       <c r="D289">
-        <v>0.009703196347031963</v>
+        <v>0.009703196347031965</v>
       </c>
     </row>
     <row r="290">
@@ -9679,7 +9679,7 @@
         <v>17</v>
       </c>
       <c r="D518">
-        <v>0.009703196347031963</v>
+        <v>0.009703196347031965</v>
       </c>
     </row>
     <row r="519">
